--- a/Digitised_Records_High_Frequency_2026_05_06.xlsx
+++ b/Digitised_Records_High_Frequency_2026_05_06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA14678-FA2F-458E-B334-EB6B8AC3D38F}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{20516951-3379-4B2C-8F4C-42D953C85CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE5E257-26CE-4F0A-B26C-59CD71412720}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="472">
   <si>
     <t>Study</t>
   </si>
@@ -1074,99 +1074,6 @@
   </si>
   <si>
     <t>San Joaquin River, Mossdale Bridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sacramento River, Weir</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sacramento River, Bryte Bend Plant</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Yolo Bypass, Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sacramento River, near Freeport</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Clarksburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sacramento River, Hood</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Yolo Bypass, Liberty Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Miner Slough 5-points</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Steamboat Slough</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Delta Cross Channel at Walnut Grove</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ryer Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Frost Slough at Montezuma Slough</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Montezuma Slough, Nurse Slough</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sacramento River at Isleton</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Roaring River, Pelican Point</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hill Slough, Grizzly Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Little Potato Slough</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mare Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Port Chicago</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> False River </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pittsburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mallard Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Piper Slough, Franks Tract</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Old River, Holland Tract</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rock Slough, at Contra Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> San Joaquin River, Stockton (McLeod Lake)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Old River, Mansion House (Victoria Isl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Old River, near Byron</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Italian Slough Mouth Near Byron</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Old River, at Head</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tom Paine Slough, Above Mouth</t>
   </si>
   <si>
     <t xml:space="preserve">Georges and Princes Pier </t>
@@ -2123,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B43C90-0725-422F-8AB9-4F021440A9B3}">
-  <dimension ref="A1:V286"/>
+  <dimension ref="A1:V255"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29" style="4" customWidth="1"/>
@@ -2165,13 +2072,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -2180,7 +2087,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -2188,7 +2095,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
@@ -2220,7 +2127,7 @@
         <v>136.16666666666666</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>10</v>
@@ -2234,7 +2141,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>18</v>
@@ -2266,7 +2173,7 @@
         <v>137.13636363636363</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>10</v>
@@ -2280,7 +2187,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>20</v>
@@ -2312,7 +2219,7 @@
         <v>135.66666666666666</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>10</v>
@@ -2357,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>10</v>
@@ -2402,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>10</v>
@@ -2447,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>10</v>
@@ -2493,7 +2400,7 @@
         <v>14</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>10</v>
@@ -2538,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>10</v>
@@ -2583,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>10</v>
@@ -2628,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>10</v>
@@ -2673,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>10</v>
@@ -2718,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>10</v>
@@ -2763,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -2808,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -2853,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>10</v>
@@ -2898,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>10</v>
@@ -2943,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>10</v>
@@ -2988,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>10</v>
@@ -3033,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>10</v>
@@ -3078,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>10</v>
@@ -3123,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
@@ -3168,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>10</v>
@@ -3213,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>10</v>
@@ -3258,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>10</v>
@@ -3303,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>10</v>
@@ -3348,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>10</v>
@@ -3393,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>10</v>
@@ -3438,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -3483,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>10</v>
@@ -3528,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>10</v>
@@ -3573,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>10</v>
@@ -3618,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>10</v>
@@ -3663,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>10</v>
@@ -3708,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>10</v>
@@ -3722,7 +3629,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>75</v>
@@ -3767,7 +3674,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>78</v>
@@ -3792,7 +3699,7 @@
         <v>103.5</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="J37" s="5">
         <v>0.5</v>
@@ -3812,7 +3719,7 @@
     </row>
     <row r="38" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>79</v>
@@ -3843,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>10</v>
@@ -3857,7 +3764,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>82</v>
@@ -3889,7 +3796,7 @@
         <v>0.97809719370294324</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>10</v>
@@ -3903,7 +3810,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>84</v>
@@ -3934,7 +3841,7 @@
         <v>18</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>10</v>
@@ -3948,7 +3855,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>87</v>
@@ -3980,7 +3887,7 @@
         <v>32</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>10</v>
@@ -3994,10 +3901,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>47</v>
@@ -4025,7 +3932,7 @@
         <v>44</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>10</v>
@@ -4039,10 +3946,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>47</v>
@@ -4070,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>10</v>
@@ -4084,10 +3991,10 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>90</v>
@@ -4116,7 +4023,7 @@
         <v>9.7365553308998543</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>10</v>
@@ -4130,7 +4037,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>93</v>
@@ -4161,7 +4068,7 @@
         <v>13</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>23</v>
@@ -4175,7 +4082,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>95</v>
@@ -4206,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>23</v>
@@ -4220,7 +4127,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>99</v>
@@ -4250,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>100</v>
@@ -4264,7 +4171,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>102</v>
@@ -4294,7 +4201,7 @@
         <v>4.8</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>100</v>
@@ -4308,7 +4215,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>98</v>
@@ -4338,7 +4245,7 @@
         <v>1.48</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>100</v>
@@ -4352,7 +4259,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>97</v>
@@ -4382,7 +4289,7 @@
         <v>1.51</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>100</v>
@@ -4396,7 +4303,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>103</v>
@@ -4426,7 +4333,7 @@
         <v>1.06</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>100</v>
@@ -4440,7 +4347,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="14" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>104</v>
@@ -4470,7 +4377,7 @@
         <v>0.35</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>100</v>
@@ -4484,7 +4391,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>105</v>
@@ -4514,7 +4421,7 @@
         <v>3</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>100</v>
@@ -4528,7 +4435,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>107</v>
@@ -4559,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>10</v>
@@ -4573,7 +4480,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>109</v>
@@ -4604,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>10</v>
@@ -4618,7 +4525,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>110</v>
@@ -4649,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>10</v>
@@ -4663,7 +4570,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>111</v>
@@ -4695,7 +4602,7 @@
         <v>18</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>10</v>
@@ -4709,7 +4616,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>113</v>
@@ -4740,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>10</v>
@@ -4754,7 +4661,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>114</v>
@@ -4785,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>10</v>
@@ -4799,7 +4706,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>116</v>
@@ -4831,7 +4738,7 @@
         <v>0.39698836413415467</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>10</v>
@@ -4845,7 +4752,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>119</v>
@@ -4877,7 +4784,7 @@
         <v>0.625</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>23</v>
@@ -4891,7 +4798,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>122</v>
@@ -4922,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>10</v>
@@ -4936,7 +4843,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>126</v>
@@ -4968,7 +4875,7 @@
         <v>0.91991786447638602</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>10</v>
@@ -4982,7 +4889,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>129</v>
@@ -5014,7 +4921,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>100</v>
@@ -5028,7 +4935,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>133</v>
@@ -5060,7 +4967,7 @@
         <v>0.99726027397260275</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>100</v>
@@ -5074,7 +4981,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>134</v>
@@ -5105,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>10</v>
@@ -5119,7 +5026,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>136</v>
@@ -5150,7 +5057,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>10</v>
@@ -5164,7 +5071,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>137</v>
@@ -5195,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>10</v>
@@ -5209,10 +5116,10 @@
     </row>
     <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="31" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="C69" s="32" t="s">
         <v>138</v>
@@ -5240,10 +5147,10 @@
         <v>34</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>16</v>
@@ -5254,7 +5161,7 @@
     </row>
     <row r="70" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="31" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>141</v>
@@ -5279,13 +5186,13 @@
         <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="J70" s="5">
         <v>39</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>10</v>
@@ -5299,7 +5206,7 @@
     </row>
     <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="31" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>143</v>
@@ -5324,14 +5231,14 @@
         <v>24</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="J71" s="5">
         <f>48+22+14</f>
         <v>84</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>10</v>
@@ -5345,7 +5252,7 @@
     </row>
     <row r="72" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="31" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>144</v>
@@ -5377,7 +5284,7 @@
         <v>148</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>10</v>
@@ -5391,7 +5298,7 @@
     </row>
     <row r="73" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="31" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B73" s="32" t="s">
         <v>146</v>
@@ -5422,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>10</v>
@@ -5436,7 +5343,7 @@
     </row>
     <row r="74" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="31" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B74" s="32" t="s">
         <v>147</v>
@@ -5467,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>10</v>
@@ -5481,7 +5388,7 @@
     </row>
     <row r="75" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="31" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>148</v>
@@ -5512,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>10</v>
@@ -5526,7 +5433,7 @@
     </row>
     <row r="76" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="31" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="B76" s="32" t="s">
         <v>148</v>
@@ -5557,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>10</v>
@@ -5571,7 +5478,7 @@
     </row>
     <row r="77" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B77" s="32" t="s">
         <v>151</v>
@@ -5602,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>23</v>
@@ -5616,7 +5523,7 @@
     </row>
     <row r="78" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B78" s="32" t="s">
         <v>153</v>
@@ -5647,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>23</v>
@@ -5661,7 +5568,7 @@
     </row>
     <row r="79" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B79" s="32" t="s">
         <v>154</v>
@@ -5692,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L79" s="9" t="s">
         <v>23</v>
@@ -5706,7 +5613,7 @@
     </row>
     <row r="80" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B80" s="32" t="s">
         <v>155</v>
@@ -5737,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>23</v>
@@ -5751,7 +5658,7 @@
     </row>
     <row r="81" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B81" s="32" t="s">
         <v>156</v>
@@ -5776,13 +5683,13 @@
         <v>45</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="J81" s="5">
         <v>9</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>23</v>
@@ -5796,7 +5703,7 @@
     </row>
     <row r="82" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B82" s="32" t="s">
         <v>157</v>
@@ -5841,7 +5748,7 @@
     </row>
     <row r="83" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B83" s="32" t="s">
         <v>158</v>
@@ -5886,7 +5793,7 @@
     </row>
     <row r="84" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B84" s="32" t="s">
         <v>159</v>
@@ -5917,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L84" s="9" t="s">
         <v>23</v>
@@ -5931,7 +5838,7 @@
     </row>
     <row r="85" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B85" s="32" t="s">
         <v>161</v>
@@ -5962,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L85" s="9" t="s">
         <v>23</v>
@@ -5976,7 +5883,7 @@
     </row>
     <row r="86" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B86" s="32" t="s">
         <v>162</v>
@@ -6007,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L86" s="9" t="s">
         <v>23</v>
@@ -6021,7 +5928,7 @@
     </row>
     <row r="87" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B87" s="32" t="s">
         <v>163</v>
@@ -6046,7 +5953,7 @@
         <v>113</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="J87" s="5">
         <v>2</v>
@@ -6066,7 +5973,7 @@
     </row>
     <row r="88" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="31" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>164</v>
@@ -6097,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L88" s="9" t="s">
         <v>23</v>
@@ -6111,7 +6018,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>165</v>
@@ -6136,7 +6043,7 @@
         <v>29</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="J89" s="5">
         <v>5</v>
@@ -6145,7 +6052,7 @@
         <v>166</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
@@ -6156,7 +6063,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>165</v>
@@ -6187,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>10</v>
@@ -6201,7 +6108,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>168</v>
@@ -6232,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>10</v>
@@ -6246,7 +6153,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>169</v>
@@ -6271,17 +6178,17 @@
         <v>17</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="J92" s="5">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>16</v>
@@ -6292,7 +6199,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>170</v>
@@ -6323,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>10</v>
@@ -6337,7 +6244,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>171</v>
@@ -6368,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>10</v>
@@ -6382,7 +6289,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B95" s="13" t="s">
         <v>173</v>
@@ -6413,7 +6320,7 @@
         <v>4</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>100</v>
@@ -6427,7 +6334,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>173</v>
@@ -6458,7 +6365,7 @@
         <v>4</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>10</v>
@@ -6472,7 +6379,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>177</v>
@@ -6503,10 +6410,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="M97" s="3" t="s">
         <v>178</v>
@@ -6517,7 +6424,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>180</v>
@@ -6548,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="M98" s="3" t="s">
         <v>178</v>
@@ -6562,7 +6469,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>181</v>
@@ -6593,10 +6500,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="M99" s="3" t="s">
         <v>178</v>
@@ -6607,7 +6514,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>182</v>
@@ -6638,10 +6545,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
@@ -6652,7 +6559,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>183</v>
@@ -6677,13 +6584,13 @@
         <v>63</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="J101" s="5">
         <v>42</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>10</v>
@@ -6697,7 +6604,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>183</v>
@@ -6722,13 +6629,13 @@
         <v>23</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="J102" s="5">
         <v>10</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>186</v>
@@ -6742,7 +6649,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>188</v>
@@ -6767,13 +6674,13 @@
         <v>37</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="J103" s="5">
         <v>29</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L103" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6694,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>190</v>
@@ -6812,14 +6719,14 @@
         <v>90</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="J104" s="5">
         <f>17+22</f>
         <v>39</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="L104" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6740,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>191</v>
@@ -6864,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>10</v>
@@ -6878,7 +6785,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>194</v>
@@ -6909,7 +6816,7 @@
         <v>58</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L106" s="3" t="s">
         <v>10</v>
@@ -6923,7 +6830,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>196</v>
@@ -6954,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L107" s="3" t="s">
         <v>10</v>
@@ -6968,7 +6875,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>197</v>
@@ -6999,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L108" s="3" t="s">
         <v>10</v>
@@ -7013,7 +6920,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>198</v>
@@ -7038,13 +6945,13 @@
         <v>71</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="J109" s="5">
         <v>38</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>10</v>
@@ -7058,7 +6965,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>199</v>
@@ -7083,13 +6990,13 @@
         <v>170</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="J110" s="5">
         <v>5</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L110" s="3" t="s">
         <v>10</v>
@@ -7103,7 +7010,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>200</v>
@@ -7134,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L111" s="3" t="s">
         <v>10</v>
@@ -7148,7 +7055,7 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>201</v>
@@ -7173,13 +7080,13 @@
         <v>60</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="J112" s="5">
         <v>71</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L112" s="3" t="s">
         <v>10</v>
@@ -7193,7 +7100,7 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>202</v>
@@ -7218,13 +7125,13 @@
         <v>10</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="J113" s="5">
         <v>59</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L113" s="3" t="s">
         <v>10</v>
@@ -7238,7 +7145,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>188</v>
@@ -7263,13 +7170,13 @@
         <v>31</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="J114" s="5">
         <v>73</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L114" s="3" t="s">
         <v>10</v>
@@ -7283,7 +7190,7 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>203</v>
@@ -7314,7 +7221,7 @@
         <v>20</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L115" s="3" t="s">
         <v>10</v>
@@ -7328,7 +7235,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>205</v>
@@ -7353,13 +7260,13 @@
         <v>53</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="J116" s="5">
         <v>2</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L116" s="3" t="s">
         <v>10</v>
@@ -7373,7 +7280,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>206</v>
@@ -7404,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L117" s="3" t="s">
         <v>10</v>
@@ -7418,7 +7325,7 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>207</v>
@@ -7449,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L118" s="3" t="s">
         <v>10</v>
@@ -7463,7 +7370,7 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>208</v>
@@ -7494,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L119" s="3" t="s">
         <v>10</v>
@@ -7508,7 +7415,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>209</v>
@@ -7539,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L120" s="3" t="s">
         <v>10</v>
@@ -7553,7 +7460,7 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>210</v>
@@ -7584,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L121" s="3" t="s">
         <v>10</v>
@@ -7598,7 +7505,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>211</v>
@@ -7629,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L122" s="3" t="s">
         <v>10</v>
@@ -7643,7 +7550,7 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>212</v>
@@ -7674,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L123" s="3" t="s">
         <v>10</v>
@@ -7688,7 +7595,7 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>213</v>
@@ -7719,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L124" s="3" t="s">
         <v>10</v>
@@ -7733,7 +7640,7 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>214</v>
@@ -7764,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L125" s="3" t="s">
         <v>10</v>
@@ -7778,7 +7685,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>215</v>
@@ -7809,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L126" s="3" t="s">
         <v>10</v>
@@ -7823,7 +7730,7 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>216</v>
@@ -7848,13 +7755,13 @@
         <v>37</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="J127" s="5">
         <v>37</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L127" s="3" t="s">
         <v>10</v>
@@ -7868,7 +7775,7 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>217</v>
@@ -7893,13 +7800,13 @@
         <v>5</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="J128" s="5">
         <v>34</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L128" s="3" t="s">
         <v>10</v>
@@ -7913,7 +7820,7 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>218</v>
@@ -7938,13 +7845,13 @@
         <v>79</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="J129" s="5">
         <v>19</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L129" s="3" t="s">
         <v>10</v>
@@ -7958,7 +7865,7 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>219</v>
@@ -7989,7 +7896,7 @@
         <v>54</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L130" s="3" t="s">
         <v>10</v>
@@ -8003,7 +7910,7 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>221</v>
@@ -8034,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L131" s="3" t="s">
         <v>10</v>
@@ -8048,7 +7955,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>222</v>
@@ -8079,7 +7986,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L132" s="3" t="s">
         <v>10</v>
@@ -8093,7 +8000,7 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>223</v>
@@ -8124,7 +8031,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L133" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8045,7 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>224</v>
@@ -8163,13 +8070,13 @@
         <v>11</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="J134" s="5">
         <v>87</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L134" s="3" t="s">
         <v>10</v>
@@ -8183,7 +8090,7 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>176</v>
@@ -8214,7 +8121,7 @@
         <v>25</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L135" s="3" t="s">
         <v>10</v>
@@ -8228,7 +8135,7 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>225</v>
@@ -8259,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L136" s="3" t="s">
         <v>10</v>
@@ -8273,7 +8180,7 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>226</v>
@@ -8304,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L137" s="3" t="s">
         <v>10</v>
@@ -8318,7 +8225,7 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>227</v>
@@ -8349,7 +8256,7 @@
         <v>30</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L138" s="3" t="s">
         <v>10</v>
@@ -8363,7 +8270,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>229</v>
@@ -8388,14 +8295,14 @@
         <v>43</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="J139" s="5">
         <f>16+8+15+12</f>
         <v>51</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L139" s="3" t="s">
         <v>10</v>
@@ -8409,7 +8316,7 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>230</v>
@@ -8440,7 +8347,7 @@
         <v>6</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L140" s="3" t="s">
         <v>10</v>
@@ -8454,7 +8361,7 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>232</v>
@@ -8485,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L141" s="3" t="s">
         <v>10</v>
@@ -8499,7 +8406,7 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>233</v>
@@ -8530,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L142" s="3" t="s">
         <v>10</v>
@@ -8544,7 +8451,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>234</v>
@@ -8575,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L143" s="3" t="s">
         <v>10</v>
@@ -8589,7 +8496,7 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>235</v>
@@ -8620,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L144" s="3" t="s">
         <v>10</v>
@@ -8634,7 +8541,7 @@
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>237</v>
@@ -8665,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L145" s="3" t="s">
         <v>10</v>
@@ -8679,7 +8586,7 @@
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>238</v>
@@ -8710,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L146" s="3" t="s">
         <v>10</v>
@@ -8724,7 +8631,7 @@
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>239</v>
@@ -8755,7 +8662,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L147" s="3" t="s">
         <v>10</v>
@@ -8769,7 +8676,7 @@
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>240</v>
@@ -8800,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L148" s="3" t="s">
         <v>10</v>
@@ -8814,7 +8721,7 @@
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>241</v>
@@ -8845,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L149" s="3" t="s">
         <v>10</v>
@@ -8859,7 +8766,7 @@
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>243</v>
@@ -8890,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L150" s="3" t="s">
         <v>10</v>
@@ -8904,7 +8811,7 @@
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>245</v>
@@ -8929,13 +8836,13 @@
         <v>2</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="J151" s="5">
         <v>32</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L151" s="3" t="s">
         <v>10</v>
@@ -8949,7 +8856,7 @@
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>246</v>
@@ -8974,13 +8881,13 @@
         <v>2</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="J152" s="5">
         <v>18</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L152" s="3" t="s">
         <v>10</v>
@@ -8994,7 +8901,7 @@
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>247</v>
@@ -9025,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L153" s="3" t="s">
         <v>10</v>
@@ -9039,7 +8946,7 @@
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>248</v>
@@ -9070,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L154" s="3" t="s">
         <v>10</v>
@@ -9084,7 +8991,7 @@
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>249</v>
@@ -9115,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L155" s="3" t="s">
         <v>10</v>
@@ -9129,7 +9036,7 @@
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>170</v>
@@ -9160,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L156" s="3" t="s">
         <v>10</v>
@@ -9174,7 +9081,7 @@
     </row>
     <row r="157" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="14" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="B157" s="15" t="s">
         <v>250</v>
@@ -9199,13 +9106,13 @@
         <v>50</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="J157" s="10">
         <v>12</v>
       </c>
       <c r="K157" s="9" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L157" s="3" t="s">
         <v>10</v>
@@ -9227,7 +9134,7 @@
     </row>
     <row r="158" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="14" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="B158" s="15" t="s">
         <v>252</v>
@@ -9252,13 +9159,13 @@
         <v>21</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="J158" s="10">
         <v>3</v>
       </c>
       <c r="K158" s="9" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L158" s="9" t="s">
         <v>23</v>
@@ -9280,7 +9187,7 @@
     </row>
     <row r="159" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="14" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="B159" s="15" t="s">
         <v>253</v>
@@ -9311,7 +9218,7 @@
         <v>0</v>
       </c>
       <c r="K159" s="9" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L159" s="9" t="s">
         <v>23</v>
@@ -9358,13 +9265,13 @@
         <v>7</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="J160" s="10">
         <v>24</v>
       </c>
       <c r="K160" s="9" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L160" s="9" t="s">
         <v>23</v>
@@ -9417,7 +9324,7 @@
         <v>1.58</v>
       </c>
       <c r="K161" s="9" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L161" s="9" t="s">
         <v>23</v>
@@ -9492,7 +9399,7 @@
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>24</v>
@@ -9523,10 +9430,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="M163" s="3" t="s">
         <v>264</v>
@@ -9537,7 +9444,7 @@
     </row>
     <row r="164" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>24</v>
@@ -9562,13 +9469,13 @@
         <v>20</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="J164" s="5">
         <v>3</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L164" s="3" t="s">
         <v>10</v>
@@ -9582,7 +9489,7 @@
     </row>
     <row r="165" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>266</v>
@@ -9607,13 +9514,13 @@
         <v>33</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="J165" s="5">
         <v>0</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L165" s="3" t="s">
         <v>267</v>
@@ -9627,7 +9534,7 @@
     </row>
     <row r="166" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>268</v>
@@ -9658,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L166" s="3" t="s">
         <v>10</v>
@@ -9672,7 +9579,7 @@
     </row>
     <row r="167" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>269</v>
@@ -9703,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L167" s="3" t="s">
         <v>10</v>
@@ -9717,7 +9624,7 @@
     </row>
     <row r="168" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>270</v>
@@ -9742,14 +9649,14 @@
         <v>5</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="J168" s="5">
         <f>98+33</f>
         <v>131</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L168" s="3" t="s">
         <v>10</v>
@@ -9763,7 +9670,7 @@
     </row>
     <row r="169" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>270</v>
@@ -9788,13 +9695,13 @@
         <v>24</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="J169" s="5">
         <v>56</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L169" s="3" t="s">
         <v>100</v>
@@ -9808,7 +9715,7 @@
     </row>
     <row r="170" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>272</v>
@@ -9839,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L170" s="3" t="s">
         <v>10</v>
@@ -9853,7 +9760,7 @@
     </row>
     <row r="171" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>272</v>
@@ -9878,14 +9785,14 @@
         <v>8</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="J171" s="5">
         <f>31+20+6</f>
         <v>57</v>
       </c>
       <c r="K171" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L171" s="3" t="s">
         <v>100</v>
@@ -9899,7 +9806,7 @@
     </row>
     <row r="172" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>273</v>
@@ -9924,13 +9831,13 @@
         <v>2</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="J172" s="5">
         <v>19</v>
       </c>
       <c r="K172" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L172" s="3" t="s">
         <v>10</v>
@@ -9944,7 +9851,7 @@
     </row>
     <row r="173" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>273</v>
@@ -9969,14 +9876,14 @@
         <v>11</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="J173" s="5">
         <f>1+30+1+18+4+4</f>
         <v>58</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L173" s="3" t="s">
         <v>100</v>
@@ -9990,7 +9897,7 @@
     </row>
     <row r="174" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>274</v>
@@ -10021,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>10</v>
@@ -10035,7 +9942,7 @@
     </row>
     <row r="175" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>277</v>
@@ -10060,14 +9967,14 @@
         <v>47.917864476386036</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="J175" s="5">
         <f>3+(30/365.25)</f>
         <v>3.0821355236139629</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L175" s="3" t="s">
         <v>10</v>
@@ -10081,7 +9988,7 @@
     </row>
     <row r="176" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>279</v>
@@ -10106,14 +10013,14 @@
         <v>51.915126625598901</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="J176" s="5">
         <f>3+((31+30+31+30)/365.25)+4-((30+31+30)/365.25)+4</f>
         <v>11.084873374401095</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L176" s="3" t="s">
         <v>10</v>
@@ -10127,7 +10034,7 @@
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B177" s="15" t="s">
         <v>280</v>
@@ -10158,7 +10065,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L177" s="3" t="s">
         <v>10</v>
@@ -10172,7 +10079,7 @@
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>282</v>
@@ -10203,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L178" s="3" t="s">
         <v>10</v>
@@ -10217,7 +10124,7 @@
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>283</v>
@@ -10242,13 +10149,13 @@
         <v>44</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="J179" s="5">
         <v>5</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L179" s="3" t="s">
         <v>10</v>
@@ -10262,7 +10169,7 @@
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>284</v>
@@ -10293,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L180" s="3" t="s">
         <v>10</v>
@@ -10307,7 +10214,7 @@
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>285</v>
@@ -10338,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="K181" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L181" s="3" t="s">
         <v>10</v>
@@ -10352,7 +10259,7 @@
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>286</v>
@@ -10377,16 +10284,16 @@
         <v>4</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="J182" s="5">
         <v>49</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="M182" s="3" t="s">
         <v>287</v>
@@ -10397,7 +10304,7 @@
     </row>
     <row r="183" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>289</v>
@@ -10428,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L183" s="3" t="s">
         <v>10</v>
@@ -10450,7 +10357,7 @@
     </row>
     <row r="184" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>291</v>
@@ -10481,7 +10388,7 @@
         <v>0</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L184" s="3" t="s">
         <v>10</v>
@@ -10503,7 +10410,7 @@
     </row>
     <row r="185" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>292</v>
@@ -10528,13 +10435,13 @@
         <v>24</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="J185" s="5">
         <v>17</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L185" s="3" t="s">
         <v>10</v>
@@ -10556,7 +10463,7 @@
     </row>
     <row r="186" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>293</v>
@@ -10581,13 +10488,13 @@
         <v>2</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="J186" s="5">
         <v>12</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L186" s="3" t="s">
         <v>10</v>
@@ -10609,7 +10516,7 @@
     </row>
     <row r="187" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>294</v>
@@ -10640,7 +10547,7 @@
         <v>0.75</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L187" s="3" t="s">
         <v>10</v>
@@ -10662,7 +10569,7 @@
     </row>
     <row r="188" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>296</v>
@@ -10693,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L188" s="3" t="s">
         <v>10</v>
@@ -10715,7 +10622,7 @@
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>297</v>
@@ -10746,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L189" s="3" t="s">
         <v>10</v>
@@ -10760,7 +10667,7 @@
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>299</v>
@@ -10791,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L190" s="3" t="s">
         <v>10</v>
@@ -10805,7 +10712,7 @@
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>300</v>
@@ -10836,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L191" s="3" t="s">
         <v>10</v>
@@ -10850,7 +10757,7 @@
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>261</v>
@@ -10881,7 +10788,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L192" s="3" t="s">
         <v>10</v>
@@ -10895,7 +10802,7 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>301</v>
@@ -10926,7 +10833,7 @@
         <v>0</v>
       </c>
       <c r="K193" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L193" s="3" t="s">
         <v>10</v>
@@ -10940,7 +10847,7 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>262</v>
@@ -10971,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L194" s="3" t="s">
         <v>10</v>
@@ -10985,7 +10892,7 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>302</v>
@@ -11010,13 +10917,13 @@
         <v>36</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="J195" s="5">
         <v>40</v>
       </c>
       <c r="K195" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L195" s="3" t="s">
         <v>10</v>
@@ -11030,7 +10937,7 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>303</v>
@@ -11061,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="K196" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L196" s="3" t="s">
         <v>10</v>
@@ -11075,7 +10982,7 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>304</v>
@@ -11106,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L197" s="3" t="s">
         <v>10</v>
@@ -11120,7 +11027,7 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>263</v>
@@ -11151,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L198" s="3" t="s">
         <v>10</v>
@@ -11165,7 +11072,7 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>305</v>
@@ -11196,7 +11103,7 @@
         <v>0</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="L199" s="3" t="s">
         <v>10</v>
@@ -11210,7 +11117,7 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>306</v>
@@ -11242,7 +11149,7 @@
         <v>0.91666666666666663</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L200" s="3" t="s">
         <v>10</v>
@@ -11256,7 +11163,7 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>307</v>
@@ -11287,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L201" s="3" t="s">
         <v>10</v>
@@ -11301,7 +11208,7 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>308</v>
@@ -11332,7 +11239,7 @@
         <v>0</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L202" s="3" t="s">
         <v>10</v>
@@ -11346,7 +11253,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>309</v>
@@ -11377,7 +11284,7 @@
         <v>0</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L203" s="3" t="s">
         <v>10</v>
@@ -11391,7 +11298,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>310</v>
@@ -11416,14 +11323,14 @@
         <v>54.5</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="J204" s="5">
         <f>6+0.5+2</f>
         <v>8.5</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L204" s="3" t="s">
         <v>100</v>
@@ -11437,7 +11344,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>310</v>
@@ -11468,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L205" s="3" t="s">
         <v>10</v>
@@ -11477,12 +11384,12 @@
         <v>16</v>
       </c>
       <c r="N205" s="7" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="B206" s="16" t="s">
         <v>313</v>
@@ -11513,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L206" s="3" t="s">
         <v>100</v>
@@ -11527,7 +11434,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>316</v>
@@ -11552,16 +11459,16 @@
         <v>35</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="J207" s="5">
         <v>4</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="M207" s="3" t="s">
         <v>16</v>
@@ -11572,7 +11479,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>316</v>
@@ -11597,13 +11504,13 @@
         <v>91</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="J208" s="5">
         <v>4</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L208" s="3" t="s">
         <v>10</v>
@@ -11617,7 +11524,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="B209" s="19" t="s">
         <v>318</v>
@@ -11649,10 +11556,10 @@
         <v>2.6468172484599588</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="M209" s="3" t="s">
         <v>16</v>
@@ -11663,7 +11570,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B210" s="20" t="s">
         <v>320</v>
@@ -11695,7 +11602,7 @@
         <v>31</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L210" s="3" t="s">
         <v>10</v>
@@ -11709,7 +11616,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B211" s="20" t="s">
         <v>322</v>
@@ -11741,7 +11648,7 @@
         <v>2</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L211" s="3" t="s">
         <v>10</v>
@@ -11755,7 +11662,7 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B212" s="20" t="s">
         <v>323</v>
@@ -11787,7 +11694,7 @@
         <v>2.8999999999999986</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L212" s="3" t="s">
         <v>10</v>
@@ -11801,7 +11708,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B213" s="20" t="s">
         <v>324</v>
@@ -11833,7 +11740,7 @@
         <v>20.099999999999994</v>
       </c>
       <c r="K213" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L213" s="3" t="s">
         <v>10</v>
@@ -11847,7 +11754,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B214" s="20" t="s">
         <v>325</v>
@@ -11879,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L214" s="3" t="s">
         <v>10</v>
@@ -11893,7 +11800,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B215" s="20" t="s">
         <v>326</v>
@@ -11925,7 +11832,7 @@
         <v>30.299999999999997</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L215" s="3" t="s">
         <v>10</v>
@@ -11939,7 +11846,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B216" s="20" t="s">
         <v>327</v>
@@ -11971,7 +11878,7 @@
         <v>16.799999999999997</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L216" s="3" t="s">
         <v>10</v>
@@ -11985,7 +11892,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B217" s="20" t="s">
         <v>328</v>
@@ -12017,7 +11924,7 @@
         <v>14.100000000000001</v>
       </c>
       <c r="K217" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L217" s="3" t="s">
         <v>10</v>
@@ -12031,7 +11938,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B218" s="19" t="s">
         <v>329</v>
@@ -12063,7 +11970,7 @@
         <v>43.2</v>
       </c>
       <c r="K218" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L218" s="3" t="s">
         <v>10</v>
@@ -12077,7 +11984,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B219" s="19" t="s">
         <v>330</v>
@@ -12109,7 +12016,7 @@
         <v>24.200000000000003</v>
       </c>
       <c r="K219" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L219" s="3" t="s">
         <v>10</v>
@@ -12123,7 +12030,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B220" s="19" t="s">
         <v>331</v>
@@ -12155,7 +12062,7 @@
         <v>15.400000000000006</v>
       </c>
       <c r="K220" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L220" s="3" t="s">
         <v>10</v>
@@ -12169,7 +12076,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B221" s="19" t="s">
         <v>332</v>
@@ -12201,7 +12108,7 @@
         <v>7.7000000000000028</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L221" s="3" t="s">
         <v>10</v>
@@ -12215,7 +12122,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B222" s="19" t="s">
         <v>333</v>
@@ -12247,7 +12154,7 @@
         <v>13</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L222" s="3" t="s">
         <v>10</v>
@@ -12261,7 +12168,7 @@
     </row>
     <row r="223" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B223" s="23" t="s">
         <v>334</v>
@@ -12293,7 +12200,7 @@
         <v>17.200000000000003</v>
       </c>
       <c r="K223" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L223" s="3" t="s">
         <v>10</v>
@@ -12307,7 +12214,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B224" s="19" t="s">
         <v>335</v>
@@ -12339,7 +12246,7 @@
         <v>7.7999999999999972</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L224" s="3" t="s">
         <v>10</v>
@@ -12353,7 +12260,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B225" s="19" t="s">
         <v>336</v>
@@ -12385,7 +12292,7 @@
         <v>14.400000000000006</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L225" s="3" t="s">
         <v>10</v>
@@ -12399,7 +12306,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B226" s="19" t="s">
         <v>337</v>
@@ -12431,7 +12338,7 @@
         <v>23.5</v>
       </c>
       <c r="K226" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L226" s="3" t="s">
         <v>10</v>
@@ -12445,7 +12352,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B227" s="19" t="s">
         <v>338</v>
@@ -12477,7 +12384,7 @@
         <v>4</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L227" s="3" t="s">
         <v>10</v>
@@ -12491,7 +12398,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B228" s="19" t="s">
         <v>339</v>
@@ -12523,7 +12430,7 @@
         <v>10.599999999999994</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L228" s="3" t="s">
         <v>10</v>
@@ -12537,7 +12444,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B229" s="19" t="s">
         <v>340</v>
@@ -12569,7 +12476,7 @@
         <v>7</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L229" s="3" t="s">
         <v>10</v>
@@ -12583,7 +12490,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B230" s="19" t="s">
         <v>341</v>
@@ -12615,7 +12522,7 @@
         <v>6</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L230" s="3" t="s">
         <v>10</v>
@@ -12629,7 +12536,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B231" s="19" t="s">
         <v>342</v>
@@ -12661,7 +12568,7 @@
         <v>6</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L231" s="3" t="s">
         <v>10</v>
@@ -12675,7 +12582,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B232" s="19" t="s">
         <v>343</v>
@@ -12707,7 +12614,7 @@
         <v>13.200000000000003</v>
       </c>
       <c r="K232" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L232" s="3" t="s">
         <v>10</v>
@@ -12721,7 +12628,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B233" s="19" t="s">
         <v>344</v>
@@ -12753,7 +12660,7 @@
         <v>5.5</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L233" s="3" t="s">
         <v>10</v>
@@ -12767,7 +12674,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="B234" s="19" t="s">
         <v>345</v>
@@ -12799,7 +12706,7 @@
         <v>58.2</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L234" s="3" t="s">
         <v>10</v>
@@ -12813,1831 +12720,467 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B235" s="24" t="s">
-        <v>346</v>
+        <v>459</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D235" s="25">
-        <v>38.608049999999999</v>
+        <v>79.919178000000002</v>
       </c>
       <c r="E235" s="25">
-        <v>-121.55929999999999</v>
-      </c>
-      <c r="F235" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G235" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H235" s="25">
-        <v>54</v>
+        <v>16.832923999999998</v>
+      </c>
+      <c r="F235" s="22">
+        <v>1900</v>
+      </c>
+      <c r="G235" s="22">
+        <v>1900</v>
+      </c>
+      <c r="H235" s="5">
+        <f>1-J235</f>
+        <v>0.29000000000000004</v>
       </c>
       <c r="I235" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J235" s="22" t="s">
-        <v>12</v>
+        <v>460</v>
+      </c>
+      <c r="J235" s="5">
+        <v>0.71</v>
       </c>
       <c r="K235" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L235" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N235" s="7" t="s">
-        <v>321</v>
+        <v>16</v>
+      </c>
+      <c r="N235" s="6" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B236" s="24" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D236" s="25">
-        <v>38.600099999999998</v>
+        <v>79.875488000000004</v>
       </c>
       <c r="E236" s="25">
-        <v>-121.53954</v>
-      </c>
-      <c r="F236" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G236" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H236" s="25">
-        <v>9</v>
+        <v>16.062946</v>
+      </c>
+      <c r="F236" s="22">
+        <v>1872</v>
+      </c>
+      <c r="G236" s="22">
+        <v>1873</v>
+      </c>
+      <c r="H236" s="5">
+        <f>2-J236</f>
+        <v>0.29000000000000004</v>
       </c>
       <c r="I236" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J236" s="22" t="s">
-        <v>12</v>
+        <v>462</v>
+      </c>
+      <c r="J236" s="5">
+        <v>1.71</v>
       </c>
       <c r="K236" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L236" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N236" s="7" t="s">
-        <v>321</v>
+        <v>463</v>
+      </c>
+      <c r="N236" s="6" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B237" s="24" t="s">
-        <v>348</v>
+        <v>464</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="D237" s="25">
-        <v>38.474780000000003</v>
+        <v>79.718778</v>
       </c>
       <c r="E237" s="25">
-        <v>-121.58823</v>
-      </c>
-      <c r="F237" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G237" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H237" s="25">
-        <v>65</v>
+        <v>10.965166</v>
+      </c>
+      <c r="F237" s="22">
+        <v>1897</v>
+      </c>
+      <c r="G237" s="22">
+        <v>1897</v>
+      </c>
+      <c r="H237" s="5">
+        <f>1-J237</f>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="I237" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J237" s="22" t="s">
-        <v>12</v>
+        <v>465</v>
+      </c>
+      <c r="J237" s="5">
+        <v>0.9</v>
       </c>
       <c r="K237" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L237" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M237" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N237" s="7" t="s">
-        <v>321</v>
+        <v>16</v>
+      </c>
+      <c r="N237" s="6" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B238" s="24" t="s">
-        <v>349</v>
+        <v>468</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D238" s="25">
-        <v>38.456110000000002</v>
-      </c>
-      <c r="E238" s="25">
-        <v>-121.5003</v>
-      </c>
-      <c r="F238" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G238" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H238" s="25">
-        <v>30</v>
-      </c>
-      <c r="I238" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J238" s="22" t="s">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="D238" s="5">
+        <v>53.4</v>
+      </c>
+      <c r="E238" s="5">
+        <v>-3</v>
+      </c>
+      <c r="F238" s="3">
+        <v>1853</v>
+      </c>
+      <c r="G238" s="3">
+        <v>1904</v>
+      </c>
+      <c r="H238" s="5">
+        <f t="shared" ref="H238:H242" si="4">(1+(G238-F238))-J238</f>
+        <v>52</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J238" s="5">
+        <v>0</v>
       </c>
       <c r="K238" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L238" s="3" t="s">
-        <v>10</v>
+        <v>398</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N238" s="7" t="s">
-        <v>321</v>
+        <v>347</v>
+      </c>
+      <c r="N238" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B239" s="24" t="s">
-        <v>350</v>
+        <v>468</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D239" s="25">
-        <v>38.417839999999998</v>
-      </c>
-      <c r="E239" s="25">
-        <v>-121.52506</v>
-      </c>
-      <c r="F239" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G239" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H239" s="25">
-        <v>29</v>
-      </c>
-      <c r="I239" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J239" s="22" t="s">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="D239" s="5">
+        <v>53.383333</v>
+      </c>
+      <c r="E239" s="5">
+        <v>-3.2166670000000002</v>
+      </c>
+      <c r="F239" s="3">
+        <v>1853</v>
+      </c>
+      <c r="G239" s="3">
+        <v>1904</v>
+      </c>
+      <c r="H239" s="5">
+        <f t="shared" si="4"/>
+        <v>52</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J239" s="5">
+        <v>0</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L239" s="3" t="s">
-        <v>10</v>
+        <v>398</v>
       </c>
       <c r="M239" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N239" s="7" t="s">
-        <v>321</v>
+        <v>347</v>
+      </c>
+      <c r="N239" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B240" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D240" s="25">
-        <v>38.36797</v>
-      </c>
-      <c r="E240" s="25">
-        <v>-121.52134</v>
-      </c>
-      <c r="F240" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G240" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H240" s="25">
-        <v>12</v>
-      </c>
-      <c r="I240" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J240" s="22" t="s">
-        <v>12</v>
+      <c r="D240" s="5">
+        <v>1.2865660000000001</v>
+      </c>
+      <c r="E240" s="5">
+        <v>103.851973</v>
+      </c>
+      <c r="F240" s="3">
+        <v>1834</v>
+      </c>
+      <c r="G240" s="3">
+        <v>1841</v>
+      </c>
+      <c r="H240" s="5">
+        <f t="shared" si="4"/>
+        <v>1.5</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J240" s="5">
+        <v>6.5</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L240" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M240" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N240" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N240" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B241" s="24" t="s">
-        <v>352</v>
+        <v>469</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D241" s="25">
-        <v>38.329279999999997</v>
-      </c>
-      <c r="E241" s="25">
-        <v>-121.69398</v>
-      </c>
-      <c r="F241" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G241" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H241" s="25">
-        <v>36</v>
-      </c>
-      <c r="I241" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J241" s="22" t="s">
-        <v>12</v>
+        <v>351</v>
+      </c>
+      <c r="D241" s="8">
+        <v>1.2669999999999999</v>
+      </c>
+      <c r="E241" s="8">
+        <v>103.85</v>
+      </c>
+      <c r="F241" s="3">
+        <v>1865</v>
+      </c>
+      <c r="G241" s="3">
+        <v>1865</v>
+      </c>
+      <c r="H241" s="5">
+        <f>(1+(G241-F241))-J241</f>
+        <v>1</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="J241" s="5">
+        <v>0</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L241" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M241" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N241" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N241" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B242" s="24" t="s">
-        <v>353</v>
+        <v>469</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D242" s="25">
-        <v>38.290120000000002</v>
-      </c>
-      <c r="E242" s="25">
-        <v>-121.64478</v>
-      </c>
-      <c r="F242" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G242" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H242" s="25">
-        <v>13</v>
-      </c>
-      <c r="I242" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J242" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K242" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L242" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M242" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N242" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A243" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B243" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D243" s="25">
-        <v>38.284999999999997</v>
-      </c>
-      <c r="E243" s="25">
-        <v>-121.587</v>
-      </c>
-      <c r="F243" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G243" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H243" s="25">
-        <v>2</v>
-      </c>
-      <c r="I243" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J243" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K243" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L243" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M243" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N243" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A244" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B244" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D244" s="25">
-        <v>38.244720000000001</v>
-      </c>
-      <c r="E244" s="25">
-        <v>-121.50528</v>
-      </c>
-      <c r="F244" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G244" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H244" s="25">
-        <v>10</v>
-      </c>
-      <c r="I244" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J244" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K244" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M244" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N244" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A245" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B245" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D245" s="25">
-        <v>38.228299999999997</v>
-      </c>
-      <c r="E245" s="25">
-        <v>-121.6722</v>
-      </c>
-      <c r="F245" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G245" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H245" s="25">
-        <v>4</v>
-      </c>
-      <c r="I245" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J245" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K245" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L245" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M245" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N245" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A246" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B246" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D246" s="25">
-        <v>38.186259999999997</v>
-      </c>
-      <c r="E246" s="25">
-        <v>-121.971</v>
-      </c>
-      <c r="F246" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G246" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H246" s="25">
-        <v>1</v>
-      </c>
-      <c r="I246" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J246" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K246" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L246" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M246" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N246" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A247" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B247" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D247" s="25">
-        <v>38.167140000000003</v>
-      </c>
-      <c r="E247" s="25">
-        <v>-121.93389000000001</v>
-      </c>
-      <c r="F247" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G247" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H247" s="25">
-        <v>1</v>
-      </c>
-      <c r="I247" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J247" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K247" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L247" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M247" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N247" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A248" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B248" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D248" s="25">
-        <v>38.163330000000002</v>
-      </c>
-      <c r="E248" s="25">
-        <v>-121.60833</v>
-      </c>
-      <c r="F248" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G248" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H248" s="25">
-        <v>19</v>
-      </c>
-      <c r="I248" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J248" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K248" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L248" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M248" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N248" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A249" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B249" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D249" s="25">
-        <v>38.110869999999998</v>
-      </c>
-      <c r="E249" s="25">
-        <v>-121.9718</v>
-      </c>
-      <c r="F249" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G249" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H249" s="25">
-        <v>5</v>
-      </c>
-      <c r="I249" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J249" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K249" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L249" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M249" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N249" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A250" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B250" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D250" s="25">
-        <v>38.108530000000002</v>
-      </c>
-      <c r="E250" s="25">
-        <v>-122.05598000000001</v>
-      </c>
-      <c r="F250" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G250" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H250" s="25">
-        <v>4</v>
-      </c>
-      <c r="I250" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J250" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K250" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L250" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M250" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N250" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A251" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B251" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="C251" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D251" s="25">
-        <v>38.09639</v>
-      </c>
-      <c r="E251" s="25">
-        <v>-121.49611</v>
-      </c>
-      <c r="F251" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G251" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H251" s="25">
-        <v>13</v>
-      </c>
-      <c r="I251" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J251" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K251" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M251" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N251" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A252" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B252" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D252" s="25">
-        <v>38.07</v>
-      </c>
-      <c r="E252" s="25">
-        <v>-122.25</v>
-      </c>
-      <c r="F252" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G252" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H252" s="25">
-        <v>20</v>
-      </c>
-      <c r="I252" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J252" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K252" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L252" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M252" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N252" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A253" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B253" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D253" s="25">
-        <v>38.056789999999999</v>
-      </c>
-      <c r="E253" s="25">
-        <v>-121.99997</v>
-      </c>
-      <c r="F253" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G253" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H253" s="25">
-        <v>1</v>
-      </c>
-      <c r="I253" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J253" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K253" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L253" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M253" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N253" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A254" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B254" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D254" s="25">
-        <v>38.055799999999998</v>
-      </c>
-      <c r="E254" s="25">
-        <v>-121.6669</v>
-      </c>
-      <c r="F254" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G254" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H254" s="25">
-        <v>2</v>
-      </c>
-      <c r="I254" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J254" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K254" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L254" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M254" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N254" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A255" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B255" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D255" s="25">
-        <v>38.042969999999997</v>
-      </c>
-      <c r="E255" s="25">
-        <v>-121.89248000000001</v>
-      </c>
-      <c r="F255" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G255" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H255" s="25">
-        <v>2</v>
-      </c>
-      <c r="I255" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J255" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K255" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M255" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N255" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A256" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B256" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D256" s="25">
-        <v>38.042700000000004</v>
-      </c>
-      <c r="E256" s="25">
-        <v>-121.92024000000001</v>
-      </c>
-      <c r="F256" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G256" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H256" s="25">
-        <v>16</v>
-      </c>
-      <c r="I256" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J256" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K256" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L256" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M256" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N256" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A257" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B257" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D257" s="25">
-        <v>38.041089999999997</v>
-      </c>
-      <c r="E257" s="25">
-        <v>-121.63218999999999</v>
-      </c>
-      <c r="F257" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G257" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H257" s="25">
-        <v>2</v>
-      </c>
-      <c r="I257" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J257" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K257" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L257" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M257" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N257" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A258" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B258" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D258" s="25">
-        <v>38.006990000000002</v>
-      </c>
-      <c r="E258" s="25">
-        <v>-121.58062</v>
-      </c>
-      <c r="F258" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G258" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H258" s="25">
-        <v>9</v>
-      </c>
-      <c r="I258" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J258" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K258" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L258" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M258" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N258" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A259" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B259" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="C259" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D259" s="25">
-        <v>37.976309999999998</v>
-      </c>
-      <c r="E259" s="25">
-        <v>-121.63760000000001</v>
-      </c>
-      <c r="F259" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G259" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H259" s="25">
-        <v>16</v>
-      </c>
-      <c r="I259" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J259" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K259" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L259" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M259" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N259" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A260" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B260" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D260" s="25">
-        <v>37.953749999999999</v>
-      </c>
-      <c r="E260" s="25">
-        <v>-121.29557</v>
-      </c>
-      <c r="F260" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G260" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H260" s="25">
-        <v>38</v>
-      </c>
-      <c r="I260" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J260" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K260" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L260" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M260" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N260" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A261" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B261" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="C261" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D261" s="25">
-        <v>37.91028</v>
-      </c>
-      <c r="E261" s="25">
-        <v>-121.56083</v>
-      </c>
-      <c r="F261" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G261" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H261" s="25">
-        <v>26</v>
-      </c>
-      <c r="I261" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J261" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K261" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L261" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M261" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N261" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A262" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B262" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D262" s="25">
-        <v>37.891039999999997</v>
-      </c>
-      <c r="E262" s="25">
-        <v>-121.57023</v>
-      </c>
-      <c r="F262" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G262" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H262" s="25">
-        <v>20</v>
-      </c>
-      <c r="I262" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J262" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K262" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L262" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M262" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N262" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A263" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B263" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D263" s="25">
-        <v>37.859929999999999</v>
-      </c>
-      <c r="E263" s="25">
-        <v>-121.58105999999999</v>
-      </c>
-      <c r="F263" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G263" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H263" s="5">
-        <v>19</v>
-      </c>
-      <c r="I263" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J263" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K263" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L263" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M263" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N263" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A264" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B264" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D264" s="25">
-        <v>37.807609999999997</v>
-      </c>
-      <c r="E264" s="25">
-        <v>-121.28128</v>
-      </c>
-      <c r="F264" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G264" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H264" s="5">
-        <v>11</v>
-      </c>
-      <c r="I264" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J264" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K264" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L264" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M264" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N264" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A265" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B265" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D265" s="25">
-        <v>37.790529999999997</v>
-      </c>
-      <c r="E265" s="25">
-        <v>-121.41862999999999</v>
-      </c>
-      <c r="F265" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G265" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H265" s="5">
-        <v>31</v>
-      </c>
-      <c r="I265" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="J265" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K265" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L265" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M265" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N265" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A266" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="B266" s="24" t="s">
-        <v>490</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D266" s="25">
-        <v>79.919178000000002</v>
-      </c>
-      <c r="E266" s="25">
-        <v>16.832923999999998</v>
-      </c>
-      <c r="F266" s="22">
-        <v>1900</v>
-      </c>
-      <c r="G266" s="22">
-        <v>1900</v>
-      </c>
-      <c r="H266" s="5">
-        <f>1-J266</f>
-        <v>0.29000000000000004</v>
-      </c>
-      <c r="I266" s="22" t="s">
-        <v>491</v>
-      </c>
-      <c r="J266" s="5">
-        <v>0.71</v>
-      </c>
-      <c r="K266" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L266" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M266" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N266" s="6" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A267" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="B267" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D267" s="25">
-        <v>79.875488000000004</v>
-      </c>
-      <c r="E267" s="25">
-        <v>16.062946</v>
-      </c>
-      <c r="F267" s="22">
-        <v>1872</v>
-      </c>
-      <c r="G267" s="22">
-        <v>1873</v>
-      </c>
-      <c r="H267" s="5">
-        <f>2-J267</f>
-        <v>0.29000000000000004</v>
-      </c>
-      <c r="I267" s="22" t="s">
-        <v>493</v>
-      </c>
-      <c r="J267" s="5">
-        <v>1.71</v>
-      </c>
-      <c r="K267" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L267" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M267" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="N267" s="6" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A268" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="B268" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D268" s="25">
-        <v>79.718778</v>
-      </c>
-      <c r="E268" s="25">
-        <v>10.965166</v>
-      </c>
-      <c r="F268" s="22">
-        <v>1897</v>
-      </c>
-      <c r="G268" s="22">
-        <v>1897</v>
-      </c>
-      <c r="H268" s="5">
-        <f>1-J268</f>
-        <v>9.9999999999999978E-2</v>
-      </c>
-      <c r="I268" s="22" t="s">
-        <v>496</v>
-      </c>
-      <c r="J268" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="K268" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L268" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M268" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N268" s="6" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A269" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D269" s="5">
-        <v>53.4</v>
-      </c>
-      <c r="E269" s="5">
-        <v>-3</v>
-      </c>
-      <c r="F269" s="3">
-        <v>1853</v>
-      </c>
-      <c r="G269" s="3">
-        <v>1904</v>
-      </c>
-      <c r="H269" s="5">
-        <f t="shared" ref="H269:H273" si="4">(1+(G269-F269))-J269</f>
-        <v>52</v>
-      </c>
-      <c r="I269" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J269" s="5">
-        <v>0</v>
-      </c>
-      <c r="K269" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="M269" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="N269" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A270" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D270" s="5">
-        <v>53.383333</v>
-      </c>
-      <c r="E270" s="5">
-        <v>-3.2166670000000002</v>
-      </c>
-      <c r="F270" s="3">
-        <v>1853</v>
-      </c>
-      <c r="G270" s="3">
-        <v>1904</v>
-      </c>
-      <c r="H270" s="5">
-        <f t="shared" si="4"/>
-        <v>52</v>
-      </c>
-      <c r="I270" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J270" s="5">
-        <v>0</v>
-      </c>
-      <c r="K270" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L270" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="M270" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="N270" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A271" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D271" s="5">
-        <v>1.2865660000000001</v>
-      </c>
-      <c r="E271" s="5">
-        <v>103.851973</v>
-      </c>
-      <c r="F271" s="3">
-        <v>1834</v>
-      </c>
-      <c r="G271" s="3">
-        <v>1841</v>
-      </c>
-      <c r="H271" s="5">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
-      </c>
-      <c r="I271" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="J271" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="K271" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L271" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M271" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N271" s="33" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A272" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D272" s="8">
-        <v>1.2669999999999999</v>
-      </c>
-      <c r="E272" s="8">
-        <v>103.85</v>
-      </c>
-      <c r="F272" s="3">
-        <v>1865</v>
-      </c>
-      <c r="G272" s="3">
-        <v>1865</v>
-      </c>
-      <c r="H272" s="5">
-        <f>(1+(G272-F272))-J272</f>
-        <v>1</v>
-      </c>
-      <c r="I272" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J272" s="5">
-        <v>0</v>
-      </c>
-      <c r="K272" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L272" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M272" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N272" s="33" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A273" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D273" s="8">
+        <v>351</v>
+      </c>
+      <c r="D242" s="8">
         <v>1.4670000000000001</v>
       </c>
-      <c r="E273" s="8">
+      <c r="E242" s="8">
         <v>103.833</v>
       </c>
-      <c r="F273" s="3">
+      <c r="F242" s="3">
         <v>1947</v>
       </c>
-      <c r="G273" s="3">
+      <c r="G242" s="3">
         <v>1947</v>
       </c>
-      <c r="H273" s="5">
+      <c r="H242" s="5">
         <f t="shared" si="4"/>
         <v>8.9999999999999969E-2</v>
       </c>
-      <c r="I273" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="J273" s="5">
+      <c r="I242" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J242" s="5">
         <v>0.91</v>
       </c>
-      <c r="K273" s="3" t="s">
+      <c r="K242" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L273" s="3" t="s">
+      <c r="L242" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M273" s="3" t="s">
+      <c r="M242" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N273" s="33" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="274" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="26"/>
-      <c r="D274" s="27"/>
-      <c r="E274" s="27"/>
-      <c r="H274" s="27"/>
-      <c r="J274" s="27"/>
-    </row>
-    <row r="275" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D275" s="27"/>
-      <c r="E275" s="27"/>
-      <c r="H275" s="27"/>
-      <c r="J275" s="27"/>
-    </row>
-    <row r="276" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="26"/>
-      <c r="D276" s="27"/>
-      <c r="E276" s="27"/>
-      <c r="H276" s="27"/>
-      <c r="J276" s="27"/>
-    </row>
-    <row r="277" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="26"/>
-      <c r="D277" s="27"/>
-      <c r="E277" s="27"/>
-      <c r="H277" s="27"/>
-      <c r="J277" s="27"/>
-    </row>
-    <row r="278" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="26"/>
-      <c r="D278" s="27"/>
-      <c r="E278" s="27"/>
-      <c r="H278" s="27"/>
-      <c r="J278" s="27"/>
-    </row>
-    <row r="279" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="26"/>
-      <c r="D279" s="27"/>
-      <c r="E279" s="27"/>
-      <c r="H279" s="27"/>
-      <c r="J279" s="27"/>
-    </row>
-    <row r="280" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="26"/>
-      <c r="D280" s="27"/>
-      <c r="E280" s="27"/>
-      <c r="H280" s="27"/>
-      <c r="J280" s="27"/>
-    </row>
-    <row r="281" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="26"/>
-      <c r="D281" s="27"/>
-      <c r="E281" s="27"/>
-      <c r="H281" s="27"/>
-      <c r="J281" s="27"/>
-    </row>
-    <row r="282" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="26"/>
-      <c r="D282" s="27"/>
-      <c r="E282" s="27"/>
-      <c r="H282" s="27"/>
-      <c r="J282" s="27"/>
-    </row>
-    <row r="283" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="26"/>
-      <c r="D283" s="27"/>
-      <c r="E283" s="27"/>
-      <c r="H283" s="27"/>
-      <c r="J283" s="27"/>
-    </row>
-    <row r="284" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="26"/>
-      <c r="D284" s="27"/>
-      <c r="E284" s="27"/>
-      <c r="H284" s="27"/>
-      <c r="J284" s="27"/>
-    </row>
-    <row r="285" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="26"/>
-      <c r="D285" s="27"/>
-      <c r="E285" s="27"/>
-      <c r="H285" s="27"/>
-      <c r="J285" s="27"/>
-    </row>
-    <row r="286" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="28"/>
-      <c r="D286" s="30"/>
-      <c r="E286" s="30"/>
-      <c r="H286" s="30"/>
-      <c r="J286" s="30"/>
-      <c r="O286"/>
-      <c r="P286"/>
-      <c r="Q286"/>
-      <c r="R286"/>
-      <c r="S286"/>
-      <c r="T286"/>
-      <c r="U286"/>
-      <c r="V286"/>
+      <c r="N242" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="243" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="26"/>
+      <c r="D243" s="27"/>
+      <c r="E243" s="27"/>
+      <c r="H243" s="27"/>
+      <c r="J243" s="27"/>
+    </row>
+    <row r="244" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D244" s="27"/>
+      <c r="E244" s="27"/>
+      <c r="H244" s="27"/>
+      <c r="J244" s="27"/>
+    </row>
+    <row r="245" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="26"/>
+      <c r="D245" s="27"/>
+      <c r="E245" s="27"/>
+      <c r="H245" s="27"/>
+      <c r="J245" s="27"/>
+    </row>
+    <row r="246" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="26"/>
+      <c r="D246" s="27"/>
+      <c r="E246" s="27"/>
+      <c r="H246" s="27"/>
+      <c r="J246" s="27"/>
+    </row>
+    <row r="247" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="26"/>
+      <c r="D247" s="27"/>
+      <c r="E247" s="27"/>
+      <c r="H247" s="27"/>
+      <c r="J247" s="27"/>
+    </row>
+    <row r="248" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="26"/>
+      <c r="D248" s="27"/>
+      <c r="E248" s="27"/>
+      <c r="H248" s="27"/>
+      <c r="J248" s="27"/>
+    </row>
+    <row r="249" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="26"/>
+      <c r="D249" s="27"/>
+      <c r="E249" s="27"/>
+      <c r="H249" s="27"/>
+      <c r="J249" s="27"/>
+    </row>
+    <row r="250" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="26"/>
+      <c r="D250" s="27"/>
+      <c r="E250" s="27"/>
+      <c r="H250" s="27"/>
+      <c r="J250" s="27"/>
+    </row>
+    <row r="251" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="26"/>
+      <c r="D251" s="27"/>
+      <c r="E251" s="27"/>
+      <c r="H251" s="27"/>
+      <c r="J251" s="27"/>
+    </row>
+    <row r="252" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="26"/>
+      <c r="D252" s="27"/>
+      <c r="E252" s="27"/>
+      <c r="H252" s="27"/>
+      <c r="J252" s="27"/>
+    </row>
+    <row r="253" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="26"/>
+      <c r="D253" s="27"/>
+      <c r="E253" s="27"/>
+      <c r="H253" s="27"/>
+      <c r="J253" s="27"/>
+    </row>
+    <row r="254" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="26"/>
+      <c r="D254" s="27"/>
+      <c r="E254" s="27"/>
+      <c r="H254" s="27"/>
+      <c r="J254" s="27"/>
+    </row>
+    <row r="255" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="28"/>
+      <c r="D255" s="30"/>
+      <c r="E255" s="30"/>
+      <c r="H255" s="30"/>
+      <c r="J255" s="30"/>
+      <c r="O255"/>
+      <c r="P255"/>
+      <c r="Q255"/>
+      <c r="R255"/>
+      <c r="S255"/>
+      <c r="T255"/>
+      <c r="U255"/>
+      <c r="V255"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="N209" r:id="rId1" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.256" xr:uid="{3B3BC2EB-07A7-4388-8DE3-0B4BE623A44F}"/>
-    <hyperlink ref="N269" r:id="rId2" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{76D41B0C-176D-4DCA-A7B0-148F54D438D6}"/>
+    <hyperlink ref="N238" r:id="rId2" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{76D41B0C-176D-4DCA-A7B0-148F54D438D6}"/>
     <hyperlink ref="N189" r:id="rId3" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{ED199385-3869-42EF-8C0C-B78D855CFBD6}"/>
     <hyperlink ref="N207" r:id="rId4" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{1EC0D7B3-38E6-4FC7-B9BD-8BE20F164A1C}"/>
     <hyperlink ref="N39" r:id="rId5" display="https://link.springer.com/article/10.1007/s10236-005-0044-z" xr:uid="{816A265D-F134-497B-A21D-C66AAD7C76C0}"/>
@@ -14740,10 +13283,10 @@
     <hyperlink ref="N190:N203" r:id="rId102" display="https://www.proquest.com/docview/2649433831?fromopenview=true&amp;pq-origsite=gscholar&amp;sourcetype=Scholarly%20Journals" xr:uid="{BDBF166A-60F1-4853-973C-5291EFBD2167}"/>
     <hyperlink ref="N205" r:id="rId103" display="https://hal.science/hal-04555208v1/file/Khan2023.pdf" xr:uid="{433F0C12-B690-43F6-A4FE-E09899D867DE}"/>
     <hyperlink ref="N208" r:id="rId104" display="https://agupubs.onlinelibrary.wiley.com/doi/full/10.1029/2024JC020908" xr:uid="{B3EF503E-80A2-4402-BBDE-9040FE69857D}"/>
-    <hyperlink ref="N211:N265" r:id="rId105" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{BF1CE461-3B84-4551-9BED-EDF762BCE6E8}"/>
-    <hyperlink ref="N270" r:id="rId106" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{5F5E2B05-7458-433E-BF1D-FB07B9D6544B}"/>
-    <hyperlink ref="N266" r:id="rId107" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{FA9A33EF-29CE-443A-8AB4-58E1AA5E65D3}"/>
-    <hyperlink ref="N267:N268" r:id="rId108" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{BDB16907-1E07-441F-8C11-FAB1E34DDCC7}"/>
+    <hyperlink ref="N211:N234" r:id="rId105" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{BF1CE461-3B84-4551-9BED-EDF762BCE6E8}"/>
+    <hyperlink ref="N239" r:id="rId106" display="https://www.zooniverse.org/projects/psmsl/uk-tides" xr:uid="{5F5E2B05-7458-433E-BF1D-FB07B9D6544B}"/>
+    <hyperlink ref="N235" r:id="rId107" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{FA9A33EF-29CE-443A-8AB4-58E1AA5E65D3}"/>
+    <hyperlink ref="N236:N237" r:id="rId108" display="https://hgss.copernicus.org/articles/17/1/2026/" xr:uid="{BDB16907-1E07-441F-8C11-FAB1E34DDCC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId109"/>
